--- a/ValueSet-mii-vs-onko-verlauf-primaertumor.xlsx
+++ b/ValueSet-mii-vs-onko-verlauf-primaertumor.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot.rc2</t>
+    <t>2027.0.0-ballot</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-09T16:49:31+00:00</t>
+    <t>2026-09-14T12:58:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-mii-vs-onko-verlauf-primaertumor.xlsx
+++ b/ValueSet-mii-vs-onko-verlauf-primaertumor.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2027.0.0-ballot</t>
+    <t>2027.0.0-ballot.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-14T12:58:08+00:00</t>
+    <t>2026-09-15T07:11:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
